--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>30/08 18:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>30/08 18:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>250</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>30/08 18:20</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>175</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>30/08 16:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>30/08 16:40</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>125</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>30/08 16:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>125</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>30/08 20:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>85</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>30/08 14:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>101</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>30/08 18:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>30/08 17:45</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>80</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>31/08 00:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>31/08 17:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>30/08 10:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>75</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>01/09 00:15</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>55</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>55</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>30/08 19:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>30/08 16:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>31/08 21:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>80</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>30/08 17:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>45</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45899.061510789</v>
+        <v>45899.06151078704</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Luleå HF –</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Luleå HF – BernEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>30/08 14:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+80,8%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45899.12329248409</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Italie – E</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Italie – EstonieCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05/09 18:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45899.12329248409</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>30/08 14:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>125</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45899.12329248409</v>
+        <v>45899.12329248842</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,97 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45899.12329248409</v>
+        <v>45899.12329248842</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | ERC Ingols</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt – KalPaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>30/08 16:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+75,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45899.14792458204</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 2.51re équipe | Wfc Minsk </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wfc Minsk – Austria VienneLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30/08 12:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+25,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45899.14792458204</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>30/08 16:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>110</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45899.14792458204</v>
+        <v>45899.14792458333</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>30/08 12:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45899.14792458204</v>
+        <v>45899.14792458333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Eisb</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KAC – Eisbären BerlinEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>30/08 18:20</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+175%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45899.18345903262</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Arthur Rin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech – Carlos AlcarazUS Open (H) - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+33,2%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45899.18345903262</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | FC Minsk (</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FC Minsk (F) – Austria Vienne (F)Europe. Ligue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>30/08 12:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+32,2%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45899.18345903262</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>30/08 18:20</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45899.18345903262</v>
+        <v>45899.18345902778</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45899.18345903262</v>
+        <v>45899.18345902778</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>30/08 12:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>26</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,52 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45899.18345903262</v>
+        <v>45899.18345902778</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Mjallby AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mjallby AIF – Halmstads BKAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>30/08 15:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+46,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45899.22142090185</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>30/08 15:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>60</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,277 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45899.22142090185</v>
+        <v>45899.22142090278</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Belfast Gi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Belfast Giants – Ilves TampereLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>30/08 18:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+191%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45899.26959497883</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ZSC Lions – TychyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>31/08 13:45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+147%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45899.26959497883</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – HC Bolzano-Bozen FoxesLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+69,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45899.26959497883</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salzbourg – Fischtown PinguinsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+49,7%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45899.26959497883</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Brynäs IFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+48,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45899.26959497883</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cesena – V</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cesena – Virtus EntellaSerie B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30/08 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+28,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45899.26959497883</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>30/08 18:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45899.26959497883</v>
+        <v>45899.26959497685</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>31/08 13:45</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45899.26959497883</v>
+        <v>45899.26959497685</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>125</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45899.26959497883</v>
+        <v>45899.26959497685</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>110</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45899.26959497883</v>
+        <v>45899.26959497685</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>110</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45899.26959497883</v>
+        <v>45899.26959497685</v>
       </c>
     </row>
     <row r="40">
@@ -2149,23 +2139,246 @@
           <t>30/08 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>55</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+28,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45899.26959497685</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – Bo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lukko – BolzanoEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+82,9%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45899.3040292173</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Brynas IFLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+53,9%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45899.3040292173</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Pinguins BremerhavenLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+52,9%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45899.3040292173</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Frölunda HC – LausanneEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+35,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45899.3040292173</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hajduk Split – HNK RijekaHNL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>31/08 19:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>+28,5%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>45899.26959497883</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+30,3%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45899.3040292173</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45899.3040292173</v>
+        <v>45899.30402921297</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>110</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45899.3040292173</v>
+        <v>45899.30402921297</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>110</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45899.3040292173</v>
+        <v>45899.30402921297</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>100</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45899.3040292173</v>
+        <v>45899.30402921297</v>
       </c>
     </row>
     <row r="45">
@@ -2362,10 +2354,8 @@
           <t>31/08 19:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2378,7 +2368,142 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45899.3040292173</v>
+        <v>45899.30402921297</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Odense BulldogsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+178%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45899.35060670192</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Olimp</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Club Olimpia – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>30/08 21:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+47,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45899.35060670192</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Frölunda HC – Lausanne HCInternational - ChampionsLeague</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>91.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+44,1%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45899.35060670192</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>225</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45899.35060670192</v>
+        <v>45899.35060670139</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>30/08 21:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45899.35060670192</v>
+        <v>45899.35060670139</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>91.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>91</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45899.35060670192</v>
+        <v>45899.35060670139</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 10.5 - tirs2e équipe | Manchester</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Manchester United – BurnleyPremier League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>30/08 14:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+31,6%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45899.38844171801</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -2526,10 +2526,8 @@
           <t>30/08 14:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.85</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45899.38844171801</v>
+        <v>45899.38844171297</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,186 @@
         <v>45899.38844171297</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Gorniczy Klub Sportowy TychyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31/08 13:45</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+190%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45899.52683782671</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | H 2 (−5.5) | T.M.Etchev</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>T.M.Etcheverry / C.Ugo Carabelli – S.Arends / L.JohnsonATP - US Open, Doubles</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>H 2 (−5.5)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+39,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45899.52683782671</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | B.Krejciko</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B.Krejcikova – T.TownsendWTA - US Open F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+32,4%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45899.52683782671</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dynamo Kie</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dynamo Kiev – FC Polissya ZhytomyrUPL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31/08 12:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+30,2%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45899.52683782671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>31/08 13:45</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>200</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45899.52683782671</v>
+        <v>45899.52683782407</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+      <c r="F51" t="n">
+        <v>4.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45899.52683782671</v>
+        <v>45899.52683782407</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.25</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45899.52683782671</v>
+        <v>45899.52683782407</v>
       </c>
     </row>
     <row r="53">
@@ -2704,10 +2698,8 @@
           <t>31/08 12:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>55</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2720,7 +2712,97 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45899.52683782671</v>
+        <v>45899.52683782407</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frolunda –</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Frolunda – LausanneLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+47,1%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45899.55832865489</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | N.Djokovic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>N.Djokovic – JL.StruffATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>40,5%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+41,8%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45899.55832865489</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -2741,10 +2741,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>90</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45899.55832865489</v>
+        <v>45899.55832865741</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3.5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45899.55832865489</v>
+        <v>45899.55832865741</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,51 @@
         <v>45899.55832865741</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Vizela </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FC Vizela – UD OliveirensePortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31/08 14:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+30,5%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45899.63816563358</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>31/08 14:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>50</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,52 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45899.63816563358</v>
+        <v>45899.63816563658</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Gornik Zab</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze – Motor LublinPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>30/08 18:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>47,2%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+28,3%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45899.68302381651</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>30/08 18:15</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.72</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,52 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45899.68302381651</v>
+        <v>45899.68302381945</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AE Larissa</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AE Larissa – AE Kifisia FCSuper League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>30/08 18:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45899.71965040034</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,23 +2913,156 @@
           <t>30/08 18:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>55</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45899.7196504051</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Antalyaspo</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Antalyaspor – Fatih KaragumrukSüper Lig</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30/08 18:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>+21,4%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>45899.71965040034</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+31,4%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45899.7687405809</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Differdang</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Differdange 03 – Jeunesse CanachLuxembourg. Luxembourg - Div. Nationale</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>31/08 16:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+20,1%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45899.7687405809</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Botafogo – Red Bull BragantinoSérie A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>30/08 21:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+19,2%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45899.7687405809</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>30/08 18:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45899.7687405809</v>
+        <v>45899.7687405787</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>31/08 16:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>15</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45899.7687405809</v>
+        <v>45899.7687405787</v>
       </c>
     </row>
     <row r="61">
@@ -3046,10 +3042,8 @@
           <t>30/08 21:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>55</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3062,7 +3056,97 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45899.7687405809</v>
+        <v>45899.7687405787</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | A.Kalinska</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A.Kalinskaya – I.SwiatekWTA - US Open F</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>30/08 23:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45899.80231043298</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – CA BelgranoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>31/08 19:45</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45899.80231043298</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>30/08 23:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45899.80231043298</v>
+        <v>45899.80231042824</v>
       </c>
     </row>
     <row r="63">
@@ -3130,23 +3128,66 @@
           <t>31/08 19:45</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>50</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45899.80231042824</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Grèce – Bi</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Grèce – BiélorussieCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>05/09 18:45</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>+15,7%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>45899.80231043298</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45899.84790236328</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>50</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,97 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45899.84790236328</v>
+        <v>45899.84790236111</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC LNZ Che</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FC LNZ Cherkasy – Veres RivneUPL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>31/08 10:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+49,1%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45899.88742408535</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Genclerbir</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Genclerbirligi – FenerbahceSüper Lig</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>31/08 16:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+35,7%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45899.88742408535</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>31/08 10:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>60</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45899.88742408535</v>
+        <v>45899.88742408565</v>
       </c>
     </row>
     <row r="66">
@@ -3259,23 +3257,156 @@
           <t>31/08 16:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>60</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+35,7%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45899.88742408565</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Nacional A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nacional Asuncion – CD RecoletaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>06/09 19:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>+35,7%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>45899.88742408535</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+91,5%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45899.92949148883</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – FK OleksandriaUPL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+41,8%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45899.92949148883</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Novi Pazar</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Novi Pazar – Etoile Rouge BelgradeSuperLiga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/08 17:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45899.92949148883</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-30.xlsx
+++ b/data/valuebets_database_2025-08-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>06/09 19:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>60</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45899.92949148883</v>
+        <v>45899.92949149306</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>55</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45899.92949148883</v>
+        <v>45899.92949149306</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>50</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,52 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45899.92949148883</v>
+        <v>45899.92949149306</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré2e équipe | FC Cincinn</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FC Cincinnati – Philadelphia UnionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>30/08 23:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45899.97130990261</v>
       </c>
     </row>
   </sheetData>
